--- a/data/trans_bre/P11_R-Edad-trans_bre.xlsx
+++ b/data/trans_bre/P11_R-Edad-trans_bre.xlsx
@@ -660,42 +660,42 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-2,96; 3,67</t>
+          <t>-2,78; 3,68</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-0,07; 6,8</t>
+          <t>-0,16; 6,54</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-1,2; 5,07</t>
+          <t>-1,13; 5,2</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-1,82; 11,78</t>
+          <t>-1,57; 10,98</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-35,46; 74,93</t>
+          <t>-32,72; 84,49</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-5,24; 152,25</t>
+          <t>-3,36; 161,57</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-24,74; 170,46</t>
+          <t>-23,9; 172,68</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-26,91; 319,05</t>
+          <t>-25,72; 285,31</t>
         </is>
       </c>
     </row>
@@ -760,42 +760,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>4,91; 11,7</t>
+          <t>4,93; 11,87</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-2,73; 3,76</t>
+          <t>-2,86; 4,0</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-1,04; 6,08</t>
+          <t>-0,96; 6,21</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-8,95; 4,46</t>
+          <t>-8,68; 4,32</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>69,4; 256,52</t>
+          <t>65,57; 257,91</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-27,69; 55,0</t>
+          <t>-28,11; 60,34</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-10,58; 91,31</t>
+          <t>-10,43; 95,47</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-47,78; 34,99</t>
+          <t>-47,0; 32,08</t>
         </is>
       </c>
     </row>
@@ -860,42 +860,42 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>5,95; 13,66</t>
+          <t>6,14; 13,9</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>2,76; 10,51</t>
+          <t>2,56; 10,54</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-0,64; 7,1</t>
+          <t>-0,64; 6,74</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-0,36; 8,38</t>
+          <t>-0,37; 8,77</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>47,77; 153,11</t>
+          <t>45,76; 155,2</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>19,51; 100,83</t>
+          <t>16,82; 102,48</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-4,55; 74,1</t>
+          <t>-5,2; 67,28</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-1,94; 50,15</t>
+          <t>-1,87; 54,68</t>
         </is>
       </c>
     </row>
@@ -960,42 +960,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>5,68; 16,77</t>
+          <t>6,45; 16,98</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>7,71; 17,47</t>
+          <t>8,21; 18,09</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>0,15; 9,23</t>
+          <t>0,26; 9,8</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>5,97; 27,83</t>
+          <t>5,53; 27,48</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>27,36; 105,6</t>
+          <t>30,93; 107,37</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>42,46; 146,44</t>
+          <t>47,45; 151,38</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>0,55; 55,91</t>
+          <t>1,01; 58,37</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>21,96; 342,05</t>
+          <t>19,52; 287,69</t>
         </is>
       </c>
     </row>
@@ -1060,42 +1060,42 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>0,84; 14,4</t>
+          <t>1,5; 15,1</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>12,62; 25,98</t>
+          <t>12,8; 25,56</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>10,69; 23,35</t>
+          <t>10,27; 22,84</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>1,81; 11,84</t>
+          <t>1,82; 11,58</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>2,73; 53,33</t>
+          <t>3,52; 54,11</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>42,75; 112,44</t>
+          <t>43,04; 110,53</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>38,52; 108,9</t>
+          <t>37,21; 104,49</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>4,45; 32,71</t>
+          <t>4,19; 31,7</t>
         </is>
       </c>
     </row>
@@ -1160,42 +1160,42 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>9,95; 24,82</t>
+          <t>9,43; 24,3</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>11,23; 27,38</t>
+          <t>11,96; 27,45</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>15,34; 29,93</t>
+          <t>14,94; 29,98</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>14,56; 52,97</t>
+          <t>14,11; 51,83</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>24,23; 74,86</t>
+          <t>22,29; 72,96</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>26,16; 78,18</t>
+          <t>26,27; 76,13</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>42,73; 106,81</t>
+          <t>40,97; 105,89</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>40,28; 171,56</t>
+          <t>37,84; 161,3</t>
         </is>
       </c>
     </row>
@@ -1260,42 +1260,42 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-1,36; 15,9</t>
+          <t>-1,22; 15,98</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>8,84; 25,17</t>
+          <t>8,98; 24,78</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>7,03; 22,3</t>
+          <t>6,79; 22,33</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>22,38; 32,4</t>
+          <t>21,68; 32,98</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-2,0; 28,79</t>
+          <t>-1,82; 28,21</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>13,25; 45,75</t>
+          <t>13,86; 46,42</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>12,36; 45,34</t>
+          <t>11,89; 44,47</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>40,46; 68,23</t>
+          <t>38,65; 70,27</t>
         </is>
       </c>
     </row>
@@ -1360,42 +1360,42 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>8,95; 13,1</t>
+          <t>8,76; 13,15</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>10,29; 14,65</t>
+          <t>10,55; 14,83</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>8,33; 12,34</t>
+          <t>8,2; 12,56</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>9,95; 25,86</t>
+          <t>10,11; 29,18</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>46,65; 76,52</t>
+          <t>45,35; 75,93</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>51,66; 81,58</t>
+          <t>53,55; 84,54</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>42,65; 70,47</t>
+          <t>41,74; 73,05</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>37,78; 118,44</t>
+          <t>36,94; 126,25</t>
         </is>
       </c>
     </row>

--- a/data/trans_bre/P11_R-Edad-trans_bre.xlsx
+++ b/data/trans_bre/P11_R-Edad-trans_bre.xlsx
@@ -627,7 +627,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>4,45</t>
+          <t>3,76</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -647,7 +647,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>66,93%</t>
+          <t>45,81%</t>
         </is>
       </c>
     </row>
@@ -660,42 +660,42 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-2,78; 3,68</t>
+          <t>-2,57; 3,88</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-0,16; 6,54</t>
+          <t>-0,27; 7,05</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-1,13; 5,2</t>
+          <t>-1,05; 5,09</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-1,57; 10,98</t>
+          <t>-2,53; 10,12</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-32,72; 84,49</t>
+          <t>-34,93; 83,1</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-3,36; 161,57</t>
+          <t>-6,15; 168,31</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-23,9; 172,68</t>
+          <t>-23,2; 175,85</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-25,72; 285,31</t>
+          <t>-21,8; 194,4</t>
         </is>
       </c>
     </row>
@@ -727,7 +727,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>-1,14</t>
+          <t>-0,17</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -747,7 +747,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>-7,45%</t>
+          <t>-1,1%</t>
         </is>
       </c>
     </row>
@@ -760,42 +760,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>4,93; 11,87</t>
+          <t>4,83; 11,55</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-2,86; 4,0</t>
+          <t>-2,75; 3,6</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-0,96; 6,21</t>
+          <t>-1,32; 5,8</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-8,68; 4,32</t>
+          <t>-5,4; 4,84</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>65,57; 257,91</t>
+          <t>64,59; 239,38</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-28,11; 60,34</t>
+          <t>-27,76; 52,07</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-10,43; 95,47</t>
+          <t>-13,31; 85,75</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-47,0; 32,08</t>
+          <t>-29,08; 39,31</t>
         </is>
       </c>
     </row>
@@ -827,7 +827,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>4,25</t>
+          <t>4,5</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -847,7 +847,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>22,66%</t>
+          <t>24,53%</t>
         </is>
       </c>
     </row>
@@ -860,42 +860,42 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>6,14; 13,9</t>
+          <t>5,67; 13,62</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>2,56; 10,54</t>
+          <t>2,65; 10,04</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-0,64; 6,74</t>
+          <t>-0,25; 6,85</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-0,37; 8,77</t>
+          <t>-0,01; 8,41</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>45,76; 155,2</t>
+          <t>41,84; 149,96</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>16,82; 102,48</t>
+          <t>18,3; 94,86</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-5,2; 67,28</t>
+          <t>-2,93; 71,49</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-1,87; 54,68</t>
+          <t>-0,02; 52,4</t>
         </is>
       </c>
     </row>
@@ -927,7 +927,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>14,57</t>
+          <t>8,31</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -947,7 +947,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>75,49%</t>
+          <t>31,72%</t>
         </is>
       </c>
     </row>
@@ -960,42 +960,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>6,45; 16,98</t>
+          <t>5,94; 16,33</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>8,21; 18,09</t>
+          <t>8,25; 17,39</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>0,26; 9,8</t>
+          <t>0,32; 9,61</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>5,53; 27,48</t>
+          <t>3,7; 12,6</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>30,93; 107,37</t>
+          <t>27,26; 100,82</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>47,45; 151,38</t>
+          <t>49,95; 144,82</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>1,01; 58,37</t>
+          <t>0,75; 59,49</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>19,52; 287,69</t>
+          <t>12,77; 52,85</t>
         </is>
       </c>
     </row>
@@ -1027,7 +1027,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>6,65</t>
+          <t>8,2</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1047,7 +1047,7 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>16,91%</t>
+          <t>21,75%</t>
         </is>
       </c>
     </row>
@@ -1060,42 +1060,42 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>1,5; 15,1</t>
+          <t>0,89; 13,96</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>12,8; 25,56</t>
+          <t>12,89; 26,23</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>10,27; 22,84</t>
+          <t>10,36; 22,57</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>1,82; 11,58</t>
+          <t>3,16; 12,73</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>3,52; 54,11</t>
+          <t>2,16; 50,62</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>43,04; 110,53</t>
+          <t>42,24; 112,68</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>37,21; 104,49</t>
+          <t>37,16; 105,51</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>4,19; 31,7</t>
+          <t>7,96; 37,41</t>
         </is>
       </c>
     </row>
@@ -1127,7 +1127,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>32,26</t>
+          <t>17,23</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1147,7 +1147,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>90,33%</t>
+          <t>49,32%</t>
         </is>
       </c>
     </row>
@@ -1160,42 +1160,42 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>9,43; 24,3</t>
+          <t>9,12; 24,41</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>11,96; 27,45</t>
+          <t>11,14; 27,95</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>14,94; 29,98</t>
+          <t>14,56; 29,35</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>14,11; 51,83</t>
+          <t>11,86; 22,29</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>22,29; 72,96</t>
+          <t>22,1; 76,46</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>26,27; 76,13</t>
+          <t>25,55; 82,72</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>40,97; 105,89</t>
+          <t>40,99; 105,0</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>37,84; 161,3</t>
+          <t>31,28; 69,87</t>
         </is>
       </c>
     </row>
@@ -1227,7 +1227,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>27,15</t>
+          <t>27,24</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -1247,7 +1247,7 @@
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>52,77%</t>
+          <t>53,58%</t>
         </is>
       </c>
     </row>
@@ -1260,42 +1260,42 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-1,22; 15,98</t>
+          <t>-1,97; 15,06</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>8,98; 24,78</t>
+          <t>9,1; 24,61</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>6,79; 22,33</t>
+          <t>7,18; 22,62</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>21,68; 32,98</t>
+          <t>21,38; 32,88</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-1,82; 28,21</t>
+          <t>-2,81; 27,53</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>13,86; 46,42</t>
+          <t>13,44; 44,4</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>11,89; 44,47</t>
+          <t>12,41; 45,55</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>38,65; 70,27</t>
+          <t>39,17; 70,5</t>
         </is>
       </c>
     </row>
@@ -1327,7 +1327,7 @@
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>15,33</t>
+          <t>10,68</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -1347,7 +1347,7 @@
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>61,63%</t>
+          <t>40,38%</t>
         </is>
       </c>
     </row>
@@ -1360,42 +1360,42 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>8,76; 13,15</t>
+          <t>9,0; 13,21</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>10,55; 14,83</t>
+          <t>10,37; 14,48</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>8,2; 12,56</t>
+          <t>8,04; 12,11</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>10,11; 29,18</t>
+          <t>8,53; 12,66</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>45,35; 75,93</t>
+          <t>46,29; 75,37</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>53,55; 84,54</t>
+          <t>51,41; 80,49</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>41,74; 73,05</t>
+          <t>41,15; 68,72</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>36,94; 126,25</t>
+          <t>30,74; 50,05</t>
         </is>
       </c>
     </row>
